--- a/DateBase/orders/Nha Thu_2026-10-7.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-7.xlsx
@@ -693,6 +693,9 @@
       <c r="C31" t="str">
         <v>572_乒乓菊白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -751,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0502015510101010169510101015141096158105681110150</v>
+        <v>05020155101010101695101010151410961581056811101515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-7.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-7.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,9 +697,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>6</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">553_嘉兰百合
+multi-colors_ gloriosa_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L33"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -754,7 +774,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05020155101010101695101010151410961581056811101515</v>
+        <v>05020155101010101695101010151410961581056811101515310</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-7.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-7.xlsx
@@ -776,6 +776,9 @@
       <c r="G2" t="str">
         <v>05020155101010101695101010151410961581056811101515310</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
